--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -136,10 +136,10 @@
     <t>普通子弹</t>
   </si>
   <si>
-    <t>Arts/Prefabs/Bullets/Bullet_Normal</t>
-  </si>
-  <si>
-    <t>Arts/UI/Gameplay/Bullets/Bullet_Normal</t>
+    <t>Arts/Bullets/Prefabs/Bullet_Normal</t>
+  </si>
+  <si>
+    <t>Arts/Bullets/UI/Bullet_Normal</t>
   </si>
   <si>
     <t>示例</t>
@@ -151,10 +151,10 @@
     <t>爆炸子弹</t>
   </si>
   <si>
-    <t>Arts/Prefabs/Bullets/Bullet_Explosive</t>
-  </si>
-  <si>
-    <t>Arts/UI/Gameplay/Bullets/Bullet_Explosive</t>
+    <t>Arts/Bullets/Prefabs/Bullet_Explosive</t>
+  </si>
+  <si>
+    <t>Arts/Bullets/UI/Bullet_Explosive</t>
   </si>
   <si>
     <t>EffectParamFloat:伤害范围</t>
@@ -166,10 +166,10 @@
     <t>高伤子弹</t>
   </si>
   <si>
-    <t>Arts/Prefabs/Bullets/Bullet_HighDamage</t>
-  </si>
-  <si>
-    <t>Arts/UI/Gameplay/Bullets/Bullet_HighDamage</t>
+    <t>Arts/Bullets/Prefabs/Bullet_HighDamage</t>
+  </si>
+  <si>
+    <t>Arts/Bullets/UI/Bullet_HighDamage</t>
   </si>
   <si>
     <t>HighSpeed</t>
@@ -178,10 +178,10 @@
     <t>高速子弹</t>
   </si>
   <si>
-    <t>Arts/Prefabs/Bullets/Bullet_HighSpeed</t>
-  </si>
-  <si>
-    <t>Arts/UI/Gameplay/Bullets/Bullet_HighSpeed</t>
+    <t>Arts/Bullets/Prefabs/Bullet_HighSpeed</t>
+  </si>
+  <si>
+    <t>Arts/Bullets/UI/Bullet_HighSpeed</t>
   </si>
 </sst>
 </file>
@@ -1358,7 +1358,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="2">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I5" s="2">
         <v>-1</v>
@@ -1397,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="I6" s="2">
         <v>-1</v>
       </c>
       <c r="J6" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>40</v>
@@ -1436,7 +1436,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="2">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I7" s="2">
         <v>-1</v>
@@ -1475,7 +1475,7 @@
         <v>8</v>
       </c>
       <c r="H8" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2">
         <v>-1</v>
@@ -1493,7 +1493,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:13">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1501,7 +1501,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:13">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>

--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -67,6 +67,9 @@
     <t>IconResourcePath</t>
   </si>
   <si>
+    <t>EffectPrefabPath</t>
+  </si>
+  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -127,6 +130,9 @@
     <t>图标资源路径</t>
   </si>
   <si>
+    <t>特效资源路径</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -142,6 +148,9 @@
     <t>Arts/Bullets/UI/Bullet_Normal</t>
   </si>
   <si>
+    <t>Arts/Effects/Prefabs/FX_Hit_01</t>
+  </si>
+  <si>
     <t>示例</t>
   </si>
   <si>
@@ -157,6 +166,9 @@
     <t>Arts/Bullets/UI/Bullet_Explosive</t>
   </si>
   <si>
+    <t>Arts/Effects/Prefabs/FX_Hit_03</t>
+  </si>
+  <si>
     <t>EffectParamFloat:伤害范围</t>
   </si>
   <si>
@@ -170,6 +182,9 @@
   </si>
   <si>
     <t>Arts/Bullets/UI/Bullet_HighDamage</t>
+  </si>
+  <si>
+    <t>Arts/Effects/Prefabs/FX_Hit_02</t>
   </si>
   <si>
     <t>HighSpeed</t>
@@ -1163,17 +1178,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25"/>
   <cols>
     <col min="1" max="10" width="28.625" style="1" customWidth="1"/>
     <col min="11" max="12" width="56.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="28.625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20.625" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="13" max="13" width="48.625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="28.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="20.625" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:13">
+    <row r="1" ht="28" customHeight="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1213,140 +1229,152 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:13">
+    <row r="2" ht="28" customHeight="1" spans="1:14">
       <c r="A2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="H2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:13">
+    <row r="3" ht="28" customHeight="1" spans="1:14">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:13">
+    <row r="4" ht="28" customHeight="1" spans="1:14">
       <c r="A4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:13">
+    <row r="5" ht="28" customHeight="1" spans="1:14">
       <c r="A5" s="4"/>
       <c r="B5" s="5">
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" s="4">
         <v>-1</v>
@@ -1367,25 +1395,28 @@
         <v>-1</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:13">
+    <row r="6" ht="28" customHeight="1" spans="1:14">
       <c r="A6" s="4"/>
       <c r="B6" s="5">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="4">
         <v>10</v>
@@ -1406,25 +1437,28 @@
         <v>3</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:13">
+    <row r="7" ht="28" customHeight="1" spans="1:14">
       <c r="A7" s="4"/>
       <c r="B7" s="5">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E7" s="4">
         <v>10</v>
@@ -1445,25 +1479,28 @@
         <v>-1</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>37</v>
+        <v>50</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:13">
+    <row r="8" ht="28" customHeight="1" spans="1:14">
       <c r="A8" s="4"/>
       <c r="B8" s="5">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E8" s="4">
         <v>10</v>
@@ -1484,16 +1521,19 @@
         <v>-1</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>37</v>
+        <v>55</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:7">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1501,7 +1541,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:7">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>

--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -1383,10 +1383,10 @@
         <v>10</v>
       </c>
       <c r="G5" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I5" s="2">
         <v>-1</v>
@@ -1425,10 +1425,10 @@
         <v>25</v>
       </c>
       <c r="G6" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I6" s="2">
         <v>-1</v>
@@ -1467,10 +1467,10 @@
         <v>50</v>
       </c>
       <c r="G7" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I7" s="2">
         <v>-1</v>
@@ -1509,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H8" s="2">
         <v>20</v>

--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -145,7 +145,7 @@
     <t>Arts/Bullets/Prefabs/Bullet_Normal</t>
   </si>
   <si>
-    <t>Arts/Bullets/UI/Bullet_Normal</t>
+    <t>Arts/UI/Sprites/Gameplay/TB_putongzidan_0001</t>
   </si>
   <si>
     <t>Arts/Effects/Prefabs/FX_Hit_01</t>
@@ -163,7 +163,7 @@
     <t>Arts/Bullets/Prefabs/Bullet_Explosive</t>
   </si>
   <si>
-    <t>Arts/Bullets/UI/Bullet_Explosive</t>
+    <t>Arts/UI/Sprites/Gameplay/TB_baozhazidan_0002</t>
   </si>
   <si>
     <t>Arts/Effects/Prefabs/FX_Hit_03</t>
@@ -181,7 +181,7 @@
     <t>Arts/Bullets/Prefabs/Bullet_HighDamage</t>
   </si>
   <si>
-    <t>Arts/Bullets/UI/Bullet_HighDamage</t>
+    <t>Arts/UI/Sprites/Gameplay/TB_gaoshangzidan_0003</t>
   </si>
   <si>
     <t>Arts/Effects/Prefabs/FX_Hit_02</t>
@@ -196,7 +196,7 @@
     <t>Arts/Bullets/Prefabs/Bullet_HighSpeed</t>
   </si>
   <si>
-    <t>Arts/Bullets/UI/Bullet_HighSpeed</t>
+    <t>Arts/UI/Sprites/Gameplay/TB_gaosuzidan_0004</t>
   </si>
 </sst>
 </file>
@@ -1533,7 +1533,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:14">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1541,7 +1541,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:14">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>

--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1386,7 +1386,7 @@
         <v>6</v>
       </c>
       <c r="H5" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I5" s="2">
         <v>-1</v>
@@ -1428,7 +1428,7 @@
         <v>2</v>
       </c>
       <c r="H6" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I6" s="2">
         <v>-1</v>
@@ -1470,7 +1470,7 @@
         <v>3</v>
       </c>
       <c r="H7" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2">
         <v>-1</v>
@@ -1533,7 +1533,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:7">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1541,7 +1541,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:7">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>

--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -142,13 +142,13 @@
     <t>普通子弹</t>
   </si>
   <si>
-    <t>Arts/Bullets/Prefabs/Bullet_Normal</t>
-  </si>
-  <si>
-    <t>Arts/UI/Sprites/Gameplay/TB_putongzidan_0001</t>
-  </si>
-  <si>
-    <t>Arts/Effects/Prefabs/FX_Hit_01</t>
+    <t>Assets/Arts/Prefabs/Bullets/pf_bullet_normal</t>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Bullet/TB_putongzidan_0001</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Effects/FX_Hit_01</t>
   </si>
   <si>
     <t>示例</t>
@@ -160,13 +160,13 @@
     <t>爆炸子弹</t>
   </si>
   <si>
-    <t>Arts/Bullets/Prefabs/Bullet_Explosive</t>
-  </si>
-  <si>
-    <t>Arts/UI/Sprites/Gameplay/TB_baozhazidan_0002</t>
-  </si>
-  <si>
-    <t>Arts/Effects/Prefabs/FX_Hit_03</t>
+    <t>Assets/Arts/Prefabs/Bullets/pf_bullet_explosive</t>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Bullet/TB_baozhazidan_0002</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Effects/FX_Hit_03</t>
   </si>
   <si>
     <t>EffectParamFloat:伤害范围</t>
@@ -178,13 +178,13 @@
     <t>高伤子弹</t>
   </si>
   <si>
-    <t>Arts/Bullets/Prefabs/Bullet_HighDamage</t>
-  </si>
-  <si>
-    <t>Arts/UI/Sprites/Gameplay/TB_gaoshangzidan_0003</t>
-  </si>
-  <si>
-    <t>Arts/Effects/Prefabs/FX_Hit_02</t>
+    <t>Assets/Arts/Prefabs/Bullets/pf_bullet_highdamage</t>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Bullet/TB_gaoshangzidan_0003</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Effects/FX_Hit_02</t>
   </si>
   <si>
     <t>HighSpeed</t>
@@ -193,10 +193,10 @@
     <t>高速子弹</t>
   </si>
   <si>
-    <t>Arts/Bullets/Prefabs/Bullet_HighSpeed</t>
-  </si>
-  <si>
-    <t>Arts/UI/Sprites/Gameplay/TB_gaosuzidan_0004</t>
+    <t>Assets/Arts/Prefabs/Bullets/pf_bullet_highspeed</t>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Bullet/TB_gaosuzidan_0004</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1182,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25"/>
   <cols>
     <col min="1" max="10" width="28.625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="56.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="56.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="76.625" style="1" customWidth="1"/>
     <col min="13" max="13" width="48.625" style="1" customWidth="1"/>
     <col min="14" max="14" width="28.625" style="1" customWidth="1"/>
     <col min="15" max="15" width="20.625" style="2" customWidth="1"/>

--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -67,7 +67,7 @@
     <t>IconResourcePath</t>
   </si>
   <si>
-    <t>EffectPrefabPath</t>
+    <t>EffectPrefabResourcePath</t>
   </si>
   <si>
     <t>Comment</t>
@@ -130,7 +130,7 @@
     <t>图标资源路径</t>
   </si>
   <si>
-    <t>特效资源路径</t>
+    <t>特效预制体资源路径</t>
   </si>
   <si>
     <t>备注</t>
@@ -178,9 +178,6 @@
     <t>高伤子弹</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Bullets/pf_bullet_highdamage</t>
-  </si>
-  <si>
     <t>Assets/Arts/UI/Sprites/Gameplay/Bullet/TB_gaoshangzidan_0003</t>
   </si>
   <si>
@@ -191,9 +188,6 @@
   </si>
   <si>
     <t>高速子弹</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Bullets/pf_bullet_highspeed</t>
   </si>
   <si>
     <t>Assets/Arts/UI/Sprites/Gameplay/Bullet/TB_gaosuzidan_0004</t>
@@ -1480,13 +1474,13 @@
         <v>-1</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>40</v>
@@ -1498,10 +1492,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="E8" s="4">
         <v>10</v>
@@ -1522,10 +1516,10 @@
         <v>-1</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>39</v>
@@ -1534,7 +1528,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:14">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1542,7 +1536,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:14">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>

--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -1381,7 +1381,7 @@
         <v>6</v>
       </c>
       <c r="H5" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" s="2">
         <v>-1</v>
@@ -1423,7 +1423,7 @@
         <v>2</v>
       </c>
       <c r="H6" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I6" s="2">
         <v>-1</v>
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="H7" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I7" s="2">
         <v>-1</v>
@@ -1507,7 +1507,7 @@
         <v>16</v>
       </c>
       <c r="H8" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I8" s="2">
         <v>-1</v>

--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1375,7 +1375,7 @@
         <v>-1</v>
       </c>
       <c r="F5" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G5" s="4">
         <v>6</v>
@@ -1417,7 +1417,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="4">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G6" s="4">
         <v>2</v>
@@ -1459,7 +1459,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="4">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G7" s="4">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="4">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G8" s="5">
         <v>16</v>
@@ -1528,7 +1528,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:7">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1536,7 +1536,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:7">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>

--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1378,10 +1378,10 @@
         <v>20</v>
       </c>
       <c r="G5" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I5" s="2">
         <v>-1</v>
@@ -1504,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="G8" s="5">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H8" s="2">
         <v>16</v>
@@ -1528,7 +1528,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:14">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1536,7 +1536,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:14">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>

--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -61,15 +61,6 @@
     <t>EffectParamFloat</t>
   </si>
   <si>
-    <t>PrefabResourcePath</t>
-  </si>
-  <si>
-    <t>IconResourcePath</t>
-  </si>
-  <si>
-    <t>EffectPrefabResourcePath</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -124,15 +115,6 @@
     <t>浮点型效果参数</t>
   </si>
   <si>
-    <t>预制体资源路径</t>
-  </si>
-  <si>
-    <t>图标资源路径</t>
-  </si>
-  <si>
-    <t>特效预制体资源路径</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
@@ -142,15 +124,6 @@
     <t>普通子弹</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Bullets/pf_bullet_normal</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Bullet/TB_putongzidan_0001</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Effects/FX_Hit_01</t>
-  </si>
-  <si>
     <t>示例</t>
   </si>
   <si>
@@ -160,15 +133,6 @@
     <t>爆炸子弹</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Bullets/pf_bullet_explosive</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Bullet/TB_baozhazidan_0002</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Effects/FX_Hit_03</t>
-  </si>
-  <si>
     <t>EffectParamFloat:伤害范围</t>
   </si>
   <si>
@@ -178,19 +142,10 @@
     <t>高伤子弹</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Bullet/TB_gaoshangzidan_0003</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Effects/FX_Hit_02</t>
-  </si>
-  <si>
     <t>HighSpeed</t>
   </si>
   <si>
     <t>高速子弹</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Bullet/TB_gaosuzidan_0004</t>
   </si>
 </sst>
 </file>
@@ -1172,19 +1127,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25"/>
   <cols>
-    <col min="1" max="10" width="28.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="56.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="76.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="48.625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="28.625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="20.625" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="1" max="2" width="28.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="48.625" style="1" customWidth="1"/>
+    <col min="4" max="11" width="28.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="20.625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:14">
+    <row r="1" ht="28" customHeight="1" spans="1:11">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1218,158 +1171,122 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:11">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:14">
-      <c r="A2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="3" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:11">
+      <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:11">
+      <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>17</v>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:14">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:14">
-      <c r="A4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:14">
+    <row r="5" ht="28" customHeight="1" spans="1:11">
       <c r="A5" s="4"/>
       <c r="B5" s="5">
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E5" s="4">
         <v>-1</v>
@@ -1389,29 +1306,20 @@
       <c r="J5" s="2">
         <v>-1</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>40</v>
+      <c r="K5" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:14">
+    <row r="6" ht="28" customHeight="1" spans="1:11">
       <c r="A6" s="4"/>
       <c r="B6" s="5">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E6" s="4">
         <v>10</v>
@@ -1431,29 +1339,20 @@
       <c r="J6" s="2">
         <v>3</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>46</v>
+      <c r="K6" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:14">
+    <row r="7" ht="28" customHeight="1" spans="1:11">
       <c r="A7" s="4"/>
       <c r="B7" s="5">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E7" s="4">
         <v>10</v>
@@ -1473,29 +1372,20 @@
       <c r="J7" s="2">
         <v>-1</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>40</v>
+      <c r="K7" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:14">
+    <row r="8" ht="28" customHeight="1" spans="1:11">
       <c r="A8" s="4"/>
       <c r="B8" s="5">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E8" s="4">
         <v>10</v>
@@ -1515,20 +1405,11 @@
       <c r="J8" s="2">
         <v>-1</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>40</v>
+      <c r="K8" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:11">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1536,7 +1417,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:11">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>

--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -122,9 +122,6 @@
   </si>
   <si>
     <t>普通子弹</t>
-  </si>
-  <si>
-    <t>示例</t>
   </si>
   <si>
     <t>Explosive</t>
@@ -1292,7 +1289,7 @@
         <v>-1</v>
       </c>
       <c r="F5" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G5" s="4">
         <v>5</v>
@@ -1306,9 +1303,7 @@
       <c r="J5" s="2">
         <v>-1</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="K5" s="4"/>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:11">
       <c r="A6" s="4"/>
@@ -1316,16 +1311,16 @@
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="E6" s="4">
         <v>10</v>
       </c>
       <c r="F6" s="4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G6" s="4">
         <v>2</v>
@@ -1340,7 +1335,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:11">
@@ -1349,16 +1344,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="E7" s="4">
         <v>10</v>
       </c>
       <c r="F7" s="4">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G7" s="4">
         <v>3</v>
@@ -1372,9 +1367,7 @@
       <c r="J7" s="2">
         <v>-1</v>
       </c>
-      <c r="K7" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="K7" s="4"/>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:11">
       <c r="A8" s="4"/>
@@ -1382,10 +1375,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="E8" s="4">
         <v>10</v>
@@ -1405,11 +1398,9 @@
       <c r="J8" s="2">
         <v>-1</v>
       </c>
-      <c r="K8" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:7">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1417,7 +1408,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:7">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
